--- a/media/exports/reports/2026-10/overtime.xlsx
+++ b/media/exports/reports/2026-10/overtime.xlsx
@@ -16,7 +16,7 @@
     <definedName name="Overtime_hours_October_so_far">'Report'!$B$9</definedName>
     <definedName name="October_last_year">'Report'!$B$10</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$46</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$C$83</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$C$71</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Data'!$5:$5</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Data'!$A$1:$E$29</definedName>
   </definedNames>
@@ -399,12 +399,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'Report'!$A$28:$A$32</f>
+              <f>'Report'!$A$28:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Report'!$B$28:$B$32</f>
+              <f>'Report'!$B$28:$B$30</f>
             </numRef>
           </val>
         </ser>
@@ -473,7 +473,7 @@
       <row>26</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2070000"/>
+    <ext cx="5400000" cy="1980000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -820,7 +820,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 6:29pm</t>
+          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 11:41pm</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>September 71.0 h</t>
+          <t>September 64.5 h</t>
         </is>
       </c>
     </row>
@@ -894,7 +894,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>46.0 h of overtime</t>
+          <t>38.0 h of overtime</t>
         </is>
       </c>
     </row>
@@ -917,7 +917,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>After-hours call-out</t>
+          <t>Installation ran over</t>
         </is>
       </c>
       <c r="B14" s="9">
@@ -928,7 +928,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Installation ran over</t>
+          <t>After-hours call-out</t>
         </is>
       </c>
       <c r="B15" s="9">
@@ -939,7 +939,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Paperwork and quotes</t>
+          <t>Short-staffed</t>
         </is>
       </c>
       <c r="B16" s="9">
@@ -996,7 +996,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Technician T1</t>
+          <t>Technician T6</t>
         </is>
       </c>
       <c r="B30" s="9">
@@ -1004,28 +1004,8 @@
         <v/>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Technician T7</t>
-        </is>
-      </c>
-      <c r="B31" s="9">
-        <f>Workings!B77</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Technician T3</t>
-        </is>
-      </c>
-      <c r="B32" s="9">
-        <f>Workings!B83</f>
-        <v/>
-      </c>
-    </row>
+    <row r="31"/>
+    <row r="32"/>
     <row r="33"/>
     <row r="34"/>
     <row r="35"/>
@@ -1051,7 +1031,7 @@
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Technicians worked 12.5 h of overtime in October so far, 11.7% of ordinary hours (target under 5.0%), against 6.2% in September. Over the last year it has gone from 4.0% to 11.7%.</t>
+          <t>Technicians worked 8.0 h of overtime in October so far, 8.1% of ordinary hours (target under 5.0%), against 5.8% in September. Over the last year it has gone from 3.9% to 8.1%.</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1046,7 @@
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>After-hours call-out is the main reason: 6.5 h, 52.0% of the overtime. Technician T5 carried the most (4.5 h). Above target by 7.2 h.</t>
+          <t>Installation ran over is the main reason: 4.0 h, 50.0% of the overtime. Technician T5 carried the most (3.5 h). Above target by 3.1 h.</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1063,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 overtime.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 6:29pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 overtime.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 11:41pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1102,7 +1082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C86"/>
+  <dimension ref="A1:C74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -1128,7 +1108,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 6:29pm</t>
+          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 11:41pm</t>
         </is>
       </c>
     </row>
@@ -1167,10 +1147,10 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>12.5</v>
+        <v>8</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>71</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="9">
@@ -1180,10 +1160,10 @@
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>106.4</v>
+        <v>98.79999999999998</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>1140.000000000001</v>
+        <v>1109.600000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1244,10 +1224,10 @@
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>12.5</v>
+        <v>8</v>
       </c>
       <c r="C17" s="13" t="n">
-        <v>71</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="18">
@@ -1257,10 +1237,10 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>106.4</v>
+        <v>98.79999999999998</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>1140.000000000001</v>
+        <v>1109.600000000001</v>
       </c>
     </row>
     <row r="19">
@@ -1316,7 +1296,7 @@
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27">
@@ -1326,7 +1306,7 @@
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>1147.600000000001</v>
+        <v>980.400000000002</v>
       </c>
     </row>
     <row r="28">
@@ -1352,7 +1332,7 @@
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>After-hours call-out: overtime, October 2026 to date</t>
+          <t>Installation ran over: overtime, October 2026 to date</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1358,7 @@
         </is>
       </c>
       <c r="B35" s="13" t="n">
-        <v>6.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
@@ -1388,7 +1368,7 @@
         </is>
       </c>
       <c r="B36" s="13" t="n">
-        <v>12.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37">
@@ -1407,7 +1387,7 @@
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>Installation ran over: overtime, October 2026 to date</t>
+          <t>After-hours call-out: overtime, October 2026 to date</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1413,7 @@
         </is>
       </c>
       <c r="B43" s="13" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -1443,7 +1423,7 @@
         </is>
       </c>
       <c r="B44" s="13" t="n">
-        <v>12.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45">
@@ -1462,7 +1442,7 @@
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>Paperwork and quotes: overtime, October 2026 to date</t>
+          <t>Short-staffed: overtime, October 2026 to date</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1468,7 @@
         </is>
       </c>
       <c r="B51" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -1498,7 +1478,7 @@
         </is>
       </c>
       <c r="B52" s="13" t="n">
-        <v>12.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="53">
@@ -1543,7 +1523,7 @@
         </is>
       </c>
       <c r="B59" s="16" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="60"/>
@@ -1585,7 +1565,7 @@
     <row r="68">
       <c r="A68" s="12" t="inlineStr">
         <is>
-          <t>Technician T1: overtime, October 2026 to date</t>
+          <t>Technician T6: overtime, October 2026 to date</t>
         </is>
       </c>
     </row>
@@ -1616,82 +1596,14 @@
     </row>
     <row r="72"/>
     <row r="73"/>
-    <row r="74">
-      <c r="A74" s="12" t="inlineStr">
-        <is>
-          <t>Technician T7: overtime, October 2026 to date</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="10" t="inlineStr">
-        <is>
-          <t>Overtime hours on this technician's shifts</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="4" t="inlineStr"/>
-      <c r="B76" s="5" t="inlineStr">
-        <is>
-          <t>Oct 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="14" t="inlineStr">
-        <is>
-          <t>Overtime hours</t>
-        </is>
-      </c>
-      <c r="B77" s="16" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80">
-      <c r="A80" s="12" t="inlineStr">
-        <is>
-          <t>Technician T3: overtime, October 2026 to date</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="10" t="inlineStr">
-        <is>
-          <t>Overtime hours on this technician's shifts</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="4" t="inlineStr"/>
-      <c r="B82" s="5" t="inlineStr">
-        <is>
-          <t>Oct 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="14" t="inlineStr">
-        <is>
-          <t>Overtime hours</t>
-        </is>
-      </c>
-      <c r="B83" s="16" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
+    <row r="74"/>
   </sheetData>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 overtime.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 6:29pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 overtime.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 11:41pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1737,7 +1649,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 6:29pm</t>
+          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 11:41pm</t>
         </is>
       </c>
     </row>
@@ -1781,10 +1693,10 @@
         </is>
       </c>
       <c r="C6" s="13" t="n">
-        <v>1094.400000000001</v>
+        <v>866.4000000000017</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>14</v>
+        <v>23.5</v>
       </c>
       <c r="E6" s="18">
         <f>IF(C6=0,"",D6/C6)</f>
@@ -1803,10 +1715,10 @@
         </is>
       </c>
       <c r="C7" s="13" t="n">
-        <v>1010.800000000002</v>
+        <v>896.8000000000018</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="E7" s="18">
         <f>IF(C7=0,"",D7/C7)</f>
@@ -1825,10 +1737,10 @@
         </is>
       </c>
       <c r="C8" s="13" t="n">
-        <v>1086.800000000001</v>
+        <v>904.4000000000018</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>24.5</v>
+        <v>27.5</v>
       </c>
       <c r="E8" s="18">
         <f>IF(C8=0,"",D8/C8)</f>
@@ -1847,10 +1759,10 @@
         </is>
       </c>
       <c r="C9" s="13" t="n">
-        <v>995.6000000000021</v>
+        <v>896.8000000000018</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>28</v>
+        <v>41.5</v>
       </c>
       <c r="E9" s="18">
         <f>IF(C9=0,"",D9/C9)</f>
@@ -1869,10 +1781,10 @@
         </is>
       </c>
       <c r="C10" s="13" t="n">
-        <v>1079.200000000001</v>
+        <v>912.0000000000018</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>26</v>
+        <v>40.5</v>
       </c>
       <c r="E10" s="18">
         <f>IF(C10=0,"",D10/C10)</f>
@@ -1891,10 +1803,10 @@
         </is>
       </c>
       <c r="C11" s="13" t="n">
-        <v>950.0000000000019</v>
+        <v>836.0000000000016</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>34.5</v>
+        <v>30.5</v>
       </c>
       <c r="E11" s="18">
         <f>IF(C11=0,"",D11/C11)</f>
@@ -1913,10 +1825,10 @@
         </is>
       </c>
       <c r="C12" s="13" t="n">
-        <v>1086.800000000001</v>
+        <v>896.8000000000018</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E12" s="18">
         <f>IF(C12=0,"",D12/C12)</f>
@@ -1935,10 +1847,10 @@
         </is>
       </c>
       <c r="C13" s="13" t="n">
-        <v>1079.200000000001</v>
+        <v>942.4000000000019</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>30</v>
+        <v>26.5</v>
       </c>
       <c r="E13" s="18">
         <f>IF(C13=0,"",D13/C13)</f>
@@ -1957,10 +1869,10 @@
         </is>
       </c>
       <c r="C14" s="13" t="n">
-        <v>1140.000000000001</v>
+        <v>1033.600000000002</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>27.5</v>
+        <v>34.5</v>
       </c>
       <c r="E14" s="18">
         <f>IF(C14=0,"",D14/C14)</f>
@@ -1979,10 +1891,10 @@
         </is>
       </c>
       <c r="C15" s="13" t="n">
-        <v>1048.800000000002</v>
+        <v>874.0000000000017</v>
       </c>
       <c r="D15" s="13" t="n">
-        <v>48.5</v>
+        <v>28.5</v>
       </c>
       <c r="E15" s="18">
         <f>IF(C15=0,"",D15/C15)</f>
@@ -2001,10 +1913,10 @@
         </is>
       </c>
       <c r="C16" s="13" t="n">
-        <v>1117.200000000001</v>
+        <v>957.600000000002</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>34</v>
+        <v>35.5</v>
       </c>
       <c r="E16" s="18">
         <f>IF(C16=0,"",D16/C16)</f>
@@ -2023,10 +1935,10 @@
         </is>
       </c>
       <c r="C17" s="13" t="n">
-        <v>1147.600000000001</v>
+        <v>980.400000000002</v>
       </c>
       <c r="D17" s="13" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E17" s="18">
         <f>IF(C17=0,"",D17/C17)</f>
@@ -2045,10 +1957,10 @@
         </is>
       </c>
       <c r="C18" s="13" t="n">
-        <v>1003.200000000002</v>
+        <v>851.2000000000016</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>39.5</v>
+        <v>32</v>
       </c>
       <c r="E18" s="18">
         <f>IF(C18=0,"",D18/C18)</f>
@@ -2067,10 +1979,10 @@
         </is>
       </c>
       <c r="C19" s="13" t="n">
-        <v>1079.200000000001</v>
+        <v>919.6000000000018</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>38</v>
+        <v>70.5</v>
       </c>
       <c r="E19" s="18">
         <f>IF(C19=0,"",D19/C19)</f>
@@ -2089,10 +2001,10 @@
         </is>
       </c>
       <c r="C20" s="13" t="n">
-        <v>1041.200000000002</v>
+        <v>1003.200000000002</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>39.5</v>
+        <v>31</v>
       </c>
       <c r="E20" s="18">
         <f>IF(C20=0,"",D20/C20)</f>
@@ -2111,10 +2023,10 @@
         </is>
       </c>
       <c r="C21" s="13" t="n">
-        <v>1010.800000000002</v>
+        <v>1026.000000000002</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>59</v>
+        <v>43.5</v>
       </c>
       <c r="E21" s="18">
         <f>IF(C21=0,"",D21/C21)</f>
@@ -2133,10 +2045,10 @@
         </is>
       </c>
       <c r="C22" s="13" t="n">
-        <v>1132.400000000001</v>
+        <v>1147.600000000001</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>63.5</v>
+        <v>48.5</v>
       </c>
       <c r="E22" s="18">
         <f>IF(C22=0,"",D22/C22)</f>
@@ -2155,10 +2067,10 @@
         </is>
       </c>
       <c r="C23" s="13" t="n">
-        <v>1041.200000000002</v>
+        <v>1033.600000000002</v>
       </c>
       <c r="D23" s="13" t="n">
-        <v>60</v>
+        <v>60.5</v>
       </c>
       <c r="E23" s="18">
         <f>IF(C23=0,"",D23/C23)</f>
@@ -2177,10 +2089,10 @@
         </is>
       </c>
       <c r="C24" s="13" t="n">
-        <v>1026.000000000002</v>
+        <v>1018.400000000002</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E24" s="18">
         <f>IF(C24=0,"",D24/C24)</f>
@@ -2199,10 +2111,10 @@
         </is>
       </c>
       <c r="C25" s="13" t="n">
-        <v>1147.600000000001</v>
+        <v>1124.800000000001</v>
       </c>
       <c r="D25" s="13" t="n">
-        <v>62.5</v>
+        <v>81</v>
       </c>
       <c r="E25" s="18">
         <f>IF(C25=0,"",D25/C25)</f>
@@ -2221,10 +2133,10 @@
         </is>
       </c>
       <c r="C26" s="13" t="n">
-        <v>1124.800000000001</v>
+        <v>1170.4</v>
       </c>
       <c r="D26" s="13" t="n">
-        <v>69.5</v>
+        <v>57.5</v>
       </c>
       <c r="E26" s="18">
         <f>IF(C26=0,"",D26/C26)</f>
@@ -2243,10 +2155,10 @@
         </is>
       </c>
       <c r="C27" s="13" t="n">
-        <v>1033.600000000002</v>
+        <v>1041.200000000002</v>
       </c>
       <c r="D27" s="13" t="n">
-        <v>53.5</v>
+        <v>58.5</v>
       </c>
       <c r="E27" s="18">
         <f>IF(C27=0,"",D27/C27)</f>
@@ -2265,10 +2177,10 @@
         </is>
       </c>
       <c r="C28" s="13" t="n">
-        <v>1140.000000000001</v>
+        <v>1109.600000000001</v>
       </c>
       <c r="D28" s="13" t="n">
-        <v>71</v>
+        <v>64.5</v>
       </c>
       <c r="E28" s="18">
         <f>IF(C28=0,"",D28/C28)</f>
@@ -2287,10 +2199,10 @@
         </is>
       </c>
       <c r="C29" s="13" t="n">
-        <v>106.4</v>
+        <v>98.79999999999998</v>
       </c>
       <c r="D29" s="13" t="n">
-        <v>12.5</v>
+        <v>8</v>
       </c>
       <c r="E29" s="18">
         <f>IF(C29=0,"",D29/C29)</f>
@@ -2303,7 +2215,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 overtime.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 6:29pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 overtime.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 11:41pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/reports/2026-10/overtime.xlsx
+++ b/media/exports/reports/2026-10/overtime.xlsx
@@ -12,10 +12,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="Overtime_October_so_far">'Report'!$B$8</definedName>
-    <definedName name="Overtime_hours_October_so_far">'Report'!$B$9</definedName>
-    <definedName name="October_last_year">'Report'!$B$10</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$46</definedName>
+    <definedName name="Overtime_October_so_far">'Report'!$B$9</definedName>
+    <definedName name="Overtime_hours_October_so_far">'Report'!$B$10</definedName>
+    <definedName name="October_last_year">'Report'!$B$11</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$47</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$C$71</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Data'!$5:$5</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Data'!$A$1:$E$29</definedName>
@@ -54,6 +54,11 @@
     <font>
       <name val="Roboto"/>
       <b val="1"/>
+      <color rgb="0025342A"/>
+    </font>
+    <font>
+      <name val="Roboto"/>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
@@ -74,11 +79,6 @@
     <font>
       <name val="Roboto"/>
       <color rgb="005F6F63"/>
-    </font>
-    <font>
-      <name val="Roboto"/>
-      <b val="1"/>
-      <color rgb="0025342A"/>
     </font>
     <font>
       <name val="Roboto"/>
@@ -116,36 +116,39 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -292,12 +295,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'Report'!$A$14:$A$16</f>
+              <f>'Report'!$A$15:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Report'!$B$14:$B$16</f>
+              <f>'Report'!$B$15:$B$17</f>
             </numRef>
           </val>
         </ser>
@@ -399,12 +402,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'Report'!$A$28:$A$30</f>
+              <f>'Report'!$A$29:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Report'!$B$28:$B$30</f>
+              <f>'Report'!$B$29:$B$31</f>
             </numRef>
           </val>
         </ser>
@@ -448,7 +451,7 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>12</row>
+      <row>13</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5400000" cy="1980000"/>
@@ -470,7 +473,7 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>27</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5400000" cy="1980000"/>
@@ -794,7 +797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -820,7 +823,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 11:41pm</t>
+          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
@@ -828,126 +831,132 @@
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
+          <t>In short: Overtime was 8.1% of ordinary hours in October so far (target under 5.0%), up from 3.9% a year earlier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
           <t>Each technician's paid hours, day by day: ordinary hours and overtime, with the main reason for the overtime.</t>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Headline number</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>Compared with</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Overtime, October so far</t>
-        </is>
-      </c>
-      <c r="B8" s="6">
-        <f>Workings!B10</f>
-        <v/>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>of ordinary hours · target under 5.0%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Overtime hours, October so far</t>
-        </is>
-      </c>
-      <c r="B9" s="6">
-        <f>Workings!B19</f>
-        <v/>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>September 64.5 h</t>
+          <t>Overtime, October so far</t>
+        </is>
+      </c>
+      <c r="B9" s="7">
+        <f>Workings!B10</f>
+        <v/>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>of ordinary hours · target under 5.0%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Overtime hours, October so far</t>
+        </is>
+      </c>
+      <c r="B10" s="9">
+        <f>Workings!B17</f>
+        <v/>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>September 64.5 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>October last year</t>
         </is>
       </c>
-      <c r="B10" s="6">
+      <c r="B11" s="7">
         <f>Workings!B28</f>
         <v/>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>38.0 h of overtime</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>Why the overtime, October 2026 to date</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr"/>
-      <c r="B13" s="5" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr"/>
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>Why the overtime</t>
         </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Installation ran over</t>
-        </is>
-      </c>
-      <c r="B14" s="9">
-        <f>Workings!B36</f>
-        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>After-hours call-out</t>
+          <t>Installation ran over</t>
         </is>
       </c>
       <c r="B15" s="9">
-        <f>Workings!B44</f>
+        <f>Workings!B35</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>After-hours call-out</t>
+        </is>
+      </c>
+      <c r="B16" s="9">
+        <f>Workings!B43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>Short-staffed</t>
         </is>
       </c>
-      <c r="B16" s="9">
-        <f>Workings!B52</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17"/>
+      <c r="B17" s="9">
+        <f>Workings!B51</f>
+        <v/>
+      </c>
+    </row>
     <row r="18"/>
     <row r="19"/>
     <row r="20"/>
@@ -956,55 +965,55 @@
     <row r="23"/>
     <row r="24"/>
     <row r="25"/>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>Overtime by technician, October 2026 to date</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr"/>
-      <c r="B27" s="5" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr"/>
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>Overtime by technician</t>
         </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Technician T5</t>
-        </is>
-      </c>
-      <c r="B28" s="9">
-        <f>Workings!B59</f>
-        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Technician T4</t>
+          <t>Technician T5</t>
         </is>
       </c>
       <c r="B29" s="9">
-        <f>Workings!B65</f>
+        <f>Workings!B59</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>Technician T4</t>
+        </is>
+      </c>
+      <c r="B30" s="9">
+        <f>Workings!B65</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>Technician T6</t>
         </is>
       </c>
-      <c r="B30" s="9">
+      <c r="B31" s="9">
         <f>Workings!B71</f>
         <v/>
       </c>
     </row>
-    <row r="31"/>
     <row r="32"/>
     <row r="33"/>
     <row r="34"/>
@@ -1013,64 +1022,66 @@
     <row r="37"/>
     <row r="38"/>
     <row r="39"/>
-    <row r="40">
-      <c r="A40" s="10" t="inlineStr">
+    <row r="40"/>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
         <is>
           <t>Overtime by month: every month is on the Data sheet.</t>
         </is>
       </c>
     </row>
-    <row r="41"/>
-    <row r="42">
-      <c r="A42" s="11" t="inlineStr">
+    <row r="42"/>
+    <row r="43">
+      <c r="A43" s="12" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>Technicians worked 8.0 h of overtime in October so far, 8.1% of ordinary hours (target under 5.0%), against 5.8% in September. Over the last year it has gone from 3.9% to 8.1%.</t>
         </is>
       </c>
     </row>
-    <row r="44"/>
-    <row r="45">
-      <c r="A45" s="11" t="inlineStr">
+    <row r="45"/>
+    <row r="46">
+      <c r="A46" s="12" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="30" customHeight="1">
-      <c r="A46" s="3" t="inlineStr">
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>Installation ran over is the main reason: 4.0 h, 50.0% of the overtime. Technician T5 carried the most (3.5 h). Above target by 3.1 h.</t>
         </is>
       </c>
     </row>
-    <row r="47"/>
     <row r="48"/>
+    <row r="49"/>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A46:D46"/>
-    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="A47:D47"/>
+    <mergeCell ref="A6:D6"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 overtime.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 11:41pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 overtime.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="25" min="0" max="16383" man="1"/>
+    <brk id="26" min="0" max="16383" man="1"/>
   </rowBreaks>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -1108,33 +1119,33 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 11:41pm</t>
+          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Overtime, October and September</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Overtime hours ÷ ordinary hours</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr"/>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr"/>
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Oct 26</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>Sep 26</t>
         </is>
@@ -1146,10 +1157,10 @@
           <t>Overtime hours</t>
         </is>
       </c>
-      <c r="B8" s="13" t="n">
+      <c r="B8" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="C8" s="13" t="n">
+      <c r="C8" s="14" t="n">
         <v>64.5</v>
       </c>
     </row>
@@ -1159,24 +1170,24 @@
           <t>Ordinary hours</t>
         </is>
       </c>
-      <c r="B9" s="13" t="n">
+      <c r="B9" s="14" t="n">
         <v>98.79999999999998</v>
       </c>
-      <c r="C9" s="13" t="n">
+      <c r="C9" s="14" t="n">
         <v>1109.600000000001</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>Share</t>
         </is>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="16">
         <f>B8/B9</f>
         <v/>
       </c>
-      <c r="C10" s="15">
+      <c r="C10" s="16">
         <f>C8/C9</f>
         <v/>
       </c>
@@ -1191,27 +1202,27 @@
     <row r="12"/>
     <row r="13"/>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>Overtime, October and September</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>Overtime hours ÷ ordinary hours</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr"/>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr"/>
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>Oct 26</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>Sep 26</t>
         </is>
@@ -1223,10 +1234,10 @@
           <t>Overtime hours</t>
         </is>
       </c>
-      <c r="B17" s="13" t="n">
+      <c r="B17" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="C17" s="13" t="n">
+      <c r="C17" s="14" t="n">
         <v>64.5</v>
       </c>
     </row>
@@ -1236,24 +1247,24 @@
           <t>Ordinary hours</t>
         </is>
       </c>
-      <c r="B18" s="13" t="n">
+      <c r="B18" s="14" t="n">
         <v>98.79999999999998</v>
       </c>
-      <c r="C18" s="13" t="n">
+      <c r="C18" s="14" t="n">
         <v>1109.600000000001</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="14" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Share</t>
         </is>
       </c>
-      <c r="B19" s="15">
+      <c r="B19" s="16">
         <f>B17/B18</f>
         <v/>
       </c>
-      <c r="C19" s="15">
+      <c r="C19" s="16">
         <f>C17/C18</f>
         <v/>
       </c>
@@ -1268,22 +1279,22 @@
     <row r="21"/>
     <row r="22"/>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>Overtime, Oct 25</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>Overtime hours ÷ ordinary hours</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr"/>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr"/>
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>Oct 25</t>
         </is>
@@ -1295,7 +1306,7 @@
           <t>Overtime hours</t>
         </is>
       </c>
-      <c r="B26" s="13" t="n">
+      <c r="B26" s="14" t="n">
         <v>38</v>
       </c>
     </row>
@@ -1305,17 +1316,17 @@
           <t>Ordinary hours</t>
         </is>
       </c>
-      <c r="B27" s="13" t="n">
+      <c r="B27" s="14" t="n">
         <v>980.400000000002</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="14" t="inlineStr">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>Overtime as a share of ordinary hours</t>
         </is>
       </c>
-      <c r="B28" s="15">
+      <c r="B28" s="16">
         <f>B26/B27</f>
         <v/>
       </c>
@@ -1330,22 +1341,22 @@
     <row r="30"/>
     <row r="31"/>
     <row r="32">
-      <c r="A32" s="12" t="inlineStr">
+      <c r="A32" s="13" t="inlineStr">
         <is>
           <t>Installation ran over: overtime, October 2026 to date</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="inlineStr">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>Overtime hours with this as the main reason</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr"/>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr"/>
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>Oct 2026</t>
         </is>
@@ -1357,7 +1368,7 @@
           <t>Overtime hours</t>
         </is>
       </c>
-      <c r="B35" s="13" t="n">
+      <c r="B35" s="14" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1367,17 +1378,17 @@
           <t>All overtime hours</t>
         </is>
       </c>
-      <c r="B36" s="13" t="n">
+      <c r="B36" s="14" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="14" t="inlineStr">
+      <c r="A37" s="15" t="inlineStr">
         <is>
           <t>Share</t>
         </is>
       </c>
-      <c r="B37" s="15">
+      <c r="B37" s="16">
         <f>B35/B36</f>
         <v/>
       </c>
@@ -1385,22 +1396,22 @@
     <row r="38"/>
     <row r="39"/>
     <row r="40">
-      <c r="A40" s="12" t="inlineStr">
+      <c r="A40" s="13" t="inlineStr">
         <is>
           <t>After-hours call-out: overtime, October 2026 to date</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="10" t="inlineStr">
+      <c r="A41" s="11" t="inlineStr">
         <is>
           <t>Overtime hours with this as the main reason</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr"/>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="A42" s="5" t="inlineStr"/>
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>Oct 2026</t>
         </is>
@@ -1412,7 +1423,7 @@
           <t>Overtime hours</t>
         </is>
       </c>
-      <c r="B43" s="13" t="n">
+      <c r="B43" s="14" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1422,17 +1433,17 @@
           <t>All overtime hours</t>
         </is>
       </c>
-      <c r="B44" s="13" t="n">
+      <c r="B44" s="14" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="14" t="inlineStr">
+      <c r="A45" s="15" t="inlineStr">
         <is>
           <t>Share</t>
         </is>
       </c>
-      <c r="B45" s="15">
+      <c r="B45" s="16">
         <f>B43/B44</f>
         <v/>
       </c>
@@ -1440,22 +1451,22 @@
     <row r="46"/>
     <row r="47"/>
     <row r="48">
-      <c r="A48" s="12" t="inlineStr">
+      <c r="A48" s="13" t="inlineStr">
         <is>
           <t>Short-staffed: overtime, October 2026 to date</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="10" t="inlineStr">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t>Overtime hours with this as the main reason</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr"/>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="A50" s="5" t="inlineStr"/>
+      <c r="B50" s="6" t="inlineStr">
         <is>
           <t>Oct 2026</t>
         </is>
@@ -1467,7 +1478,7 @@
           <t>Overtime hours</t>
         </is>
       </c>
-      <c r="B51" s="13" t="n">
+      <c r="B51" s="14" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1477,17 +1488,17 @@
           <t>All overtime hours</t>
         </is>
       </c>
-      <c r="B52" s="13" t="n">
+      <c r="B52" s="14" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="14" t="inlineStr">
+      <c r="A53" s="15" t="inlineStr">
         <is>
           <t>Share</t>
         </is>
       </c>
-      <c r="B53" s="15">
+      <c r="B53" s="16">
         <f>B51/B52</f>
         <v/>
       </c>
@@ -1495,102 +1506,102 @@
     <row r="54"/>
     <row r="55"/>
     <row r="56">
-      <c r="A56" s="12" t="inlineStr">
+      <c r="A56" s="13" t="inlineStr">
         <is>
           <t>Technician T5: overtime, October 2026 to date</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="10" t="inlineStr">
+      <c r="A57" s="11" t="inlineStr">
         <is>
           <t>Overtime hours on this technician's shifts</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="inlineStr"/>
-      <c r="B58" s="5" t="inlineStr">
+      <c r="A58" s="5" t="inlineStr"/>
+      <c r="B58" s="6" t="inlineStr">
         <is>
           <t>Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="14" t="inlineStr">
+      <c r="A59" s="15" t="inlineStr">
         <is>
           <t>Overtime hours</t>
         </is>
       </c>
-      <c r="B59" s="16" t="n">
+      <c r="B59" s="17" t="n">
         <v>3.5</v>
       </c>
     </row>
     <row r="60"/>
     <row r="61"/>
     <row r="62">
-      <c r="A62" s="12" t="inlineStr">
+      <c r="A62" s="13" t="inlineStr">
         <is>
           <t>Technician T4: overtime, October 2026 to date</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="10" t="inlineStr">
+      <c r="A63" s="11" t="inlineStr">
         <is>
           <t>Overtime hours on this technician's shifts</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="inlineStr"/>
-      <c r="B64" s="5" t="inlineStr">
+      <c r="A64" s="5" t="inlineStr"/>
+      <c r="B64" s="6" t="inlineStr">
         <is>
           <t>Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="14" t="inlineStr">
+      <c r="A65" s="15" t="inlineStr">
         <is>
           <t>Overtime hours</t>
         </is>
       </c>
-      <c r="B65" s="16" t="n">
+      <c r="B65" s="17" t="n">
         <v>2.5</v>
       </c>
     </row>
     <row r="66"/>
     <row r="67"/>
     <row r="68">
-      <c r="A68" s="12" t="inlineStr">
+      <c r="A68" s="13" t="inlineStr">
         <is>
           <t>Technician T6: overtime, October 2026 to date</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="10" t="inlineStr">
+      <c r="A69" s="11" t="inlineStr">
         <is>
           <t>Overtime hours on this technician's shifts</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="4" t="inlineStr"/>
-      <c r="B70" s="5" t="inlineStr">
+      <c r="A70" s="5" t="inlineStr"/>
+      <c r="B70" s="6" t="inlineStr">
         <is>
           <t>Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="14" t="inlineStr">
+      <c r="A71" s="15" t="inlineStr">
         <is>
           <t>Overtime hours</t>
         </is>
       </c>
-      <c r="B71" s="16" t="n">
+      <c r="B71" s="17" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1603,7 +1614,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 overtime.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 11:41pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 overtime.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1649,562 +1660,562 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 11:41pm</t>
+          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Ordinary hours</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Overtime hours</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Overtime share</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>Nov 24</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C6" s="13" t="n">
+      <c r="C6" s="14" t="n">
         <v>866.4000000000017</v>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="14" t="n">
         <v>23.5</v>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="19">
         <f>IF(C6=0,"",D6/C6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>Dec 24</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C7" s="13" t="n">
+      <c r="C7" s="14" t="n">
         <v>896.8000000000018</v>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="14" t="n">
         <v>19.5</v>
       </c>
-      <c r="E7" s="18">
+      <c r="E7" s="19">
         <f>IF(C7=0,"",D7/C7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>Jan 25</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C8" s="13" t="n">
+      <c r="C8" s="14" t="n">
         <v>904.4000000000018</v>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="14" t="n">
         <v>27.5</v>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="19">
         <f>IF(C8=0,"",D8/C8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t>Feb 25</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C9" s="13" t="n">
+      <c r="C9" s="14" t="n">
         <v>896.8000000000018</v>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D9" s="14" t="n">
         <v>41.5</v>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="19">
         <f>IF(C9=0,"",D9/C9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>Mar 25</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C10" s="13" t="n">
+      <c r="C10" s="14" t="n">
         <v>912.0000000000018</v>
       </c>
-      <c r="D10" s="13" t="n">
+      <c r="D10" s="14" t="n">
         <v>40.5</v>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="19">
         <f>IF(C10=0,"",D10/C10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>Apr 25</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C11" s="13" t="n">
+      <c r="C11" s="14" t="n">
         <v>836.0000000000016</v>
       </c>
-      <c r="D11" s="13" t="n">
+      <c r="D11" s="14" t="n">
         <v>30.5</v>
       </c>
-      <c r="E11" s="18">
+      <c r="E11" s="19">
         <f>IF(C11=0,"",D11/C11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>May 25</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C12" s="13" t="n">
+      <c r="C12" s="14" t="n">
         <v>896.8000000000018</v>
       </c>
-      <c r="D12" s="13" t="n">
+      <c r="D12" s="14" t="n">
         <v>33</v>
       </c>
-      <c r="E12" s="18">
+      <c r="E12" s="19">
         <f>IF(C12=0,"",D12/C12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C13" s="13" t="n">
+      <c r="C13" s="14" t="n">
         <v>942.4000000000019</v>
       </c>
-      <c r="D13" s="13" t="n">
+      <c r="D13" s="14" t="n">
         <v>26.5</v>
       </c>
-      <c r="E13" s="18">
+      <c r="E13" s="19">
         <f>IF(C13=0,"",D13/C13)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>Jul 25</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C14" s="13" t="n">
+      <c r="C14" s="14" t="n">
         <v>1033.600000000002</v>
       </c>
-      <c r="D14" s="13" t="n">
+      <c r="D14" s="14" t="n">
         <v>34.5</v>
       </c>
-      <c r="E14" s="18">
+      <c r="E14" s="19">
         <f>IF(C14=0,"",D14/C14)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="18" t="inlineStr">
         <is>
           <t>Aug 25</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C15" s="13" t="n">
+      <c r="C15" s="14" t="n">
         <v>874.0000000000017</v>
       </c>
-      <c r="D15" s="13" t="n">
+      <c r="D15" s="14" t="n">
         <v>28.5</v>
       </c>
-      <c r="E15" s="18">
+      <c r="E15" s="19">
         <f>IF(C15=0,"",D15/C15)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C16" s="13" t="n">
+      <c r="C16" s="14" t="n">
         <v>957.600000000002</v>
       </c>
-      <c r="D16" s="13" t="n">
+      <c r="D16" s="14" t="n">
         <v>35.5</v>
       </c>
-      <c r="E16" s="18">
+      <c r="E16" s="19">
         <f>IF(C16=0,"",D16/C16)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C17" s="13" t="n">
+      <c r="C17" s="14" t="n">
         <v>980.400000000002</v>
       </c>
-      <c r="D17" s="13" t="n">
+      <c r="D17" s="14" t="n">
         <v>38</v>
       </c>
-      <c r="E17" s="18">
+      <c r="E17" s="19">
         <f>IF(C17=0,"",D17/C17)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C18" s="13" t="n">
+      <c r="C18" s="14" t="n">
         <v>851.2000000000016</v>
       </c>
-      <c r="D18" s="13" t="n">
+      <c r="D18" s="14" t="n">
         <v>32</v>
       </c>
-      <c r="E18" s="18">
+      <c r="E18" s="19">
         <f>IF(C18=0,"",D18/C18)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="18" t="inlineStr">
         <is>
           <t>Dec 25</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C19" s="13" t="n">
+      <c r="C19" s="14" t="n">
         <v>919.6000000000018</v>
       </c>
-      <c r="D19" s="13" t="n">
+      <c r="D19" s="14" t="n">
         <v>70.5</v>
       </c>
-      <c r="E19" s="18">
+      <c r="E19" s="19">
         <f>IF(C19=0,"",D19/C19)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="17" t="inlineStr">
+      <c r="A20" s="18" t="inlineStr">
         <is>
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B20" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C20" s="13" t="n">
+      <c r="C20" s="14" t="n">
         <v>1003.200000000002</v>
       </c>
-      <c r="D20" s="13" t="n">
+      <c r="D20" s="14" t="n">
         <v>31</v>
       </c>
-      <c r="E20" s="18">
+      <c r="E20" s="19">
         <f>IF(C20=0,"",D20/C20)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="17" t="inlineStr">
+      <c r="A21" s="18" t="inlineStr">
         <is>
           <t>Feb 26</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C21" s="13" t="n">
+      <c r="C21" s="14" t="n">
         <v>1026.000000000002</v>
       </c>
-      <c r="D21" s="13" t="n">
+      <c r="D21" s="14" t="n">
         <v>43.5</v>
       </c>
-      <c r="E21" s="18">
+      <c r="E21" s="19">
         <f>IF(C21=0,"",D21/C21)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="18" t="inlineStr">
         <is>
           <t>Mar 26</t>
         </is>
       </c>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B22" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C22" s="13" t="n">
+      <c r="C22" s="14" t="n">
         <v>1147.600000000001</v>
       </c>
-      <c r="D22" s="13" t="n">
+      <c r="D22" s="14" t="n">
         <v>48.5</v>
       </c>
-      <c r="E22" s="18">
+      <c r="E22" s="19">
         <f>IF(C22=0,"",D22/C22)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="inlineStr">
+      <c r="A23" s="18" t="inlineStr">
         <is>
           <t>Apr 26</t>
         </is>
       </c>
-      <c r="B23" s="17" t="inlineStr">
+      <c r="B23" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C23" s="13" t="n">
+      <c r="C23" s="14" t="n">
         <v>1033.600000000002</v>
       </c>
-      <c r="D23" s="13" t="n">
+      <c r="D23" s="14" t="n">
         <v>60.5</v>
       </c>
-      <c r="E23" s="18">
+      <c r="E23" s="19">
         <f>IF(C23=0,"",D23/C23)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="17" t="inlineStr">
+      <c r="A24" s="18" t="inlineStr">
         <is>
           <t>May 26</t>
         </is>
       </c>
-      <c r="B24" s="17" t="inlineStr">
+      <c r="B24" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C24" s="13" t="n">
+      <c r="C24" s="14" t="n">
         <v>1018.400000000002</v>
       </c>
-      <c r="D24" s="13" t="n">
+      <c r="D24" s="14" t="n">
         <v>68</v>
       </c>
-      <c r="E24" s="18">
+      <c r="E24" s="19">
         <f>IF(C24=0,"",D24/C24)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="17" t="inlineStr">
+      <c r="A25" s="18" t="inlineStr">
         <is>
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="B25" s="17" t="inlineStr">
+      <c r="B25" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C25" s="13" t="n">
+      <c r="C25" s="14" t="n">
         <v>1124.800000000001</v>
       </c>
-      <c r="D25" s="13" t="n">
+      <c r="D25" s="14" t="n">
         <v>81</v>
       </c>
-      <c r="E25" s="18">
+      <c r="E25" s="19">
         <f>IF(C25=0,"",D25/C25)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="17" t="inlineStr">
+      <c r="A26" s="18" t="inlineStr">
         <is>
           <t>Jul 26</t>
         </is>
       </c>
-      <c r="B26" s="17" t="inlineStr">
+      <c r="B26" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C26" s="13" t="n">
+      <c r="C26" s="14" t="n">
         <v>1170.4</v>
       </c>
-      <c r="D26" s="13" t="n">
+      <c r="D26" s="14" t="n">
         <v>57.5</v>
       </c>
-      <c r="E26" s="18">
+      <c r="E26" s="19">
         <f>IF(C26=0,"",D26/C26)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="18" t="inlineStr">
         <is>
           <t>Aug 26</t>
         </is>
       </c>
-      <c r="B27" s="17" t="inlineStr">
+      <c r="B27" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C27" s="13" t="n">
+      <c r="C27" s="14" t="n">
         <v>1041.200000000002</v>
       </c>
-      <c r="D27" s="13" t="n">
+      <c r="D27" s="14" t="n">
         <v>58.5</v>
       </c>
-      <c r="E27" s="18">
+      <c r="E27" s="19">
         <f>IF(C27=0,"",D27/C27)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="17" t="inlineStr">
+      <c r="A28" s="18" t="inlineStr">
         <is>
           <t>Sep 26</t>
         </is>
       </c>
-      <c r="B28" s="17" t="inlineStr">
+      <c r="B28" s="18" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C28" s="13" t="n">
+      <c r="C28" s="14" t="n">
         <v>1109.600000000001</v>
       </c>
-      <c r="D28" s="13" t="n">
+      <c r="D28" s="14" t="n">
         <v>64.5</v>
       </c>
-      <c r="E28" s="18">
+      <c r="E28" s="19">
         <f>IF(C28=0,"",D28/C28)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="17" t="inlineStr">
+      <c r="A29" s="18" t="inlineStr">
         <is>
           <t>Oct 26</t>
         </is>
       </c>
-      <c r="B29" s="17" t="inlineStr">
+      <c r="B29" s="18" t="inlineStr">
         <is>
           <t>Incomplete</t>
         </is>
       </c>
-      <c r="C29" s="13" t="n">
+      <c r="C29" s="14" t="n">
         <v>98.79999999999998</v>
       </c>
-      <c r="D29" s="13" t="n">
+      <c r="D29" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="E29" s="18">
+      <c r="E29" s="19">
         <f>IF(C29=0,"",D29/C29)</f>
         <v/>
       </c>
@@ -2215,7 +2226,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 overtime.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 11:41pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 overtime.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
